--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/752fb57b23291faf/문서/contest/wind_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_2B59D2BFD3E0DD524542D1F050D4C0366D91F7E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49525FC2-E7E9-4BF8-9DE9-EE6973174E0A}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2B59D2BFD3C0D10E8562C8F050FA30F667B1FB90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D798728-48D7-4965-8454-F6EB4E954E50}"/>
   <bookViews>
-    <workbookView xWindow="8000" yWindow="4550" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8340" yWindow="4890" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>Timestamp</t>
   </si>
@@ -67,6 +67,9 @@
     <t>베이스라인 모듈화 및 로거 연동 테스트</t>
   </si>
   <si>
+    <t>2026-07-22 22:32:01</t>
+  </si>
+  <si>
     <t>v2</t>
   </si>
   <si>
@@ -79,7 +82,28 @@
     <t>LightGBM 교체 / 100m 고도 바람 변수 및 풍향(Wind Direction) 피처 추가</t>
   </si>
   <si>
-    <t>2026-07-22 22:32:01</t>
+    <t>2026-07-23 00:47:32</t>
+  </si>
+  <si>
+    <t>v3</t>
+  </si>
+  <si>
+    <t>5-Fold CV 도입 / 달력 피처 + GFS (80m/100m) 합성 풍속, v^3, 풍향</t>
+  </si>
+  <si>
+    <t>5-Fold OOF 평가 / K-Fold 교차 검증 적용으로 오버피팅 없는 OOF 점수 산출</t>
+  </si>
+  <si>
+    <t>2026-07-23 01:17:00</t>
+  </si>
+  <si>
+    <t>v4</t>
+  </si>
+  <si>
+    <t>격자별 Pivot 피처 + GFS/LDAPS 117m 멱법칙 보정 풍속 + 풍향 sin/cos 변환(360도와 1도의 경계 불연속 문제 해결) + SimpleImputer 제거(LightGBM 결측치 자체학습)</t>
+  </si>
+  <si>
+    <t>5-Fold OOF 평가 / v4: 공간 피처 확장, 117m 허브고도 보정, 무한대(inf) -&gt; nan 변환 적용</t>
   </si>
 </sst>
 </file>
@@ -435,19 +459,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="65.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="66.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="80.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -516,10 +531,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>0.79930000000000001</v>
@@ -531,19 +546,83 @@
         <v>0.66300000000000003</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>42</v>
       </c>
       <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <v>0.60208994459999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>0.68640000000000001</v>
+      </c>
+      <c r="D4">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="E4">
+        <v>0.4708</v>
+      </c>
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.60208994459999998</v>
+      <c r="G4">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4">
+        <v>0.60569102330000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>0.68859999999999999</v>
+      </c>
+      <c r="D5">
+        <v>0.90259999999999996</v>
+      </c>
+      <c r="E5">
+        <v>0.47449999999999998</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.61370839420000001</v>
       </c>
     </row>
   </sheetData>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/752fb57b23291faf/문서/contest/wind_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2B59D2BFD3C0D10E8562C8F050FA30F667B1FB90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D798728-48D7-4965-8454-F6EB4E954E50}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_2B59D2BFD320D2423143C7F050C208F65C15F962" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76CCE0FE-A6AD-4EBF-B37A-BC33538E59CF}"/>
   <bookViews>
     <workbookView xWindow="8340" yWindow="4890" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Timestamp</t>
   </si>
@@ -104,6 +104,18 @@
   </si>
   <si>
     <t>5-Fold OOF 평가 / v4: 공간 피처 확장, 117m 허브고도 보정, 무한대(inf) -&gt; nan 변환 적용</t>
+  </si>
+  <si>
+    <t>2026-07-23 01:46:47</t>
+  </si>
+  <si>
+    <t>v5</t>
+  </si>
+  <si>
+    <t>v4 피처 + 푄현상(높새바람) 지수 + 열돔/대기정체 지수 + 시계열 Ramp(Diff/Rolling) 변동성</t>
+  </si>
+  <si>
+    <t>5-Fold OOF 평가 / v5: 태백 특수 기상 현상(푄/열돔) 및 시계열 바람 변동성 반영</t>
   </si>
 </sst>
 </file>
@@ -459,10 +471,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="9" max="9" width="80.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -621,8 +634,40 @@
       <c r="I5" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5">
         <v>0.61370839420000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="D6">
+        <v>0.90249999999999997</v>
+      </c>
+      <c r="E6">
+        <v>0.47360000000000002</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.61517095129999999</v>
       </c>
     </row>
   </sheetData>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/752fb57b23291faf/문서/contest/wind_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2B59D2BFD320D2423143C7F050C208F65C15F962" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76CCE0FE-A6AD-4EBF-B37A-BC33538E59CF}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_2B59D2BFD320D2423143C7F050C208F65C15F962" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E45213F6-4CD7-43A9-ABAF-BCA1AB96F3FB}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="4890" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="3910" windowWidth="36270" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,15 +28,6 @@
     <t>Version</t>
   </si>
   <si>
-    <t>Total Score</t>
-  </si>
-  <si>
-    <t>1 - NMAE</t>
-  </si>
-  <si>
-    <t>FICR</t>
-  </si>
-  <si>
     <t>Model</t>
   </si>
   <si>
@@ -49,9 +40,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Public Score</t>
-  </si>
-  <si>
     <t>2026-07-22 22:06:44</t>
   </si>
   <si>
@@ -116,13 +104,45 @@
   </si>
   <si>
     <t>5-Fold OOF 평가 / v5: 태백 특수 기상 현상(푄/열돔) 및 시계열 바람 변동성 반영</t>
+  </si>
+  <si>
+    <t>Val_Total Score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Val_1 - NMAE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Val_FICR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leaderboard_Score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leaderboard_1-nMAE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leaderboard_FiCR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8639447416	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3402351475	</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,20 +158,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8.25"/>
+      <color rgb="FF485465"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF485465"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -166,9 +198,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -184,6 +224,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,14 +515,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="149.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="80.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.4140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,36 +540,42 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
       </c>
       <c r="C2">
         <v>0.7137</v>
@@ -527,27 +587,33 @@
         <v>0.51259999999999994</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2">
         <v>0.5932059435</v>
       </c>
+      <c r="K2" s="2">
+        <v>0.86146538110000004</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.32494650590000002</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0.79930000000000001</v>
@@ -559,27 +625,33 @@
         <v>0.66300000000000003</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2">
         <v>0.60208994459999998</v>
       </c>
+      <c r="K3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>0.68640000000000001</v>
@@ -591,27 +663,33 @@
         <v>0.4708</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2">
         <v>0.60569102330000002</v>
       </c>
+      <c r="K4" s="2">
+        <v>0.86602318869999995</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.34535885789999998</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>0.68859999999999999</v>
@@ -623,27 +701,34 @@
         <v>0.47449999999999998</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5">
+        <v>23</v>
+      </c>
+      <c r="J5" s="2">
         <v>0.61370839420000001</v>
       </c>
+      <c r="K5" s="2">
+        <v>0.87077697679999999</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.35663981150000001</v>
+      </c>
+      <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>0.68799999999999994</v>
@@ -655,20 +740,27 @@
         <v>0.47360000000000002</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="1">
+        <v>27</v>
+      </c>
+      <c r="J6" s="2">
         <v>0.61517095129999999</v>
       </c>
+      <c r="K6" s="3">
+        <v>0.8708219358</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.35951996679999998</v>
+      </c>
+      <c r="M6" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/752fb57b23291faf/문서/contest/wind_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_2B59D2BFD320D2423143C7F050C208F65C15F962" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E45213F6-4CD7-43A9-ABAF-BCA1AB96F3FB}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_2B59D2BFD370D55035E0D9F0509718755DD5E2DC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894A9AE0-A1FE-464B-BC9E-263056E358BA}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="3910" windowWidth="36270" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6910" yWindow="5050" windowWidth="36270" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,6 +28,15 @@
     <t>Version</t>
   </si>
   <si>
+    <t>Val_Total Score</t>
+  </si>
+  <si>
+    <t>Val_1 - NMAE</t>
+  </si>
+  <si>
+    <t>Val_FICR</t>
+  </si>
+  <si>
     <t>Model</t>
   </si>
   <si>
@@ -40,6 +49,18 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Leaderboard_Score</t>
+  </si>
+  <si>
+    <t>Leaderboard_1-nMAE</t>
+  </si>
+  <si>
+    <t>Leaderboard_FiCR</t>
+  </si>
+  <si>
+    <t>Execution Time (sec)</t>
+  </si>
+  <si>
     <t>2026-07-22 22:06:44</t>
   </si>
   <si>
@@ -106,35 +127,30 @@
     <t>5-Fold OOF 평가 / v5: 태백 특수 기상 현상(푄/열돔) 및 시계열 바람 변동성 반영</t>
   </si>
   <si>
-    <t>Val_Total Score</t>
+    <t>2026-07-25 21:58:16</t>
+  </si>
+  <si>
+    <t>v6</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>v5 피처 + WPD/850hPa/De-rating/푄현상 등 6대 도메인 피처 + 35개 Pruning + Nelder-Mead 후처리</t>
+  </si>
+  <si>
+    <t>5-Fold GroupKFold(월별) / Nelder-Mead 후처리 적용 (+0.0542)</t>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Val_1 - NMAE</t>
+    <t>Environment Spec</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Val_FICR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leaderboard_Score</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leaderboard_1-nMAE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leaderboard_FiCR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8639447416	</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3402351475	</t>
+    <t>CPU: AMD Ryzen 9 7950X | GPU: RTX 4080 SUPER | RAM: DDR5 64GB</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -142,7 +158,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,18 +174,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.25"/>
+      <sz val="11"/>
       <color rgb="FF485465"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -198,17 +208,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -515,24 +520,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.4140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="149.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="80.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.4140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.58203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.58203125" customWidth="1"/>
+    <col min="14" max="14" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,42 +541,48 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="L1" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>0.7137</v>
@@ -587,33 +594,39 @@
         <v>0.51259999999999994</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="2">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2">
         <v>0.5932059435</v>
       </c>
-      <c r="K2" s="2">
+      <c r="M2">
         <v>0.86146538110000004</v>
       </c>
-      <c r="L2" s="2">
+      <c r="N2">
         <v>0.32494650590000002</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>0.79930000000000001</v>
@@ -625,33 +638,36 @@
         <v>0.66300000000000003</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="2">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3">
         <v>0.60208994459999998</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
+      <c r="M3">
+        <v>0.86394474160000001</v>
+      </c>
+      <c r="N3">
+        <v>0.3402351475</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0.68640000000000001</v>
@@ -663,33 +679,36 @@
         <v>0.4708</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G4">
         <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="2">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4">
         <v>0.60569102330000002</v>
       </c>
-      <c r="K4" s="2">
+      <c r="M4">
         <v>0.86602318869999995</v>
       </c>
-      <c r="L4" s="2">
+      <c r="N4">
         <v>0.34535885789999998</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>0.68859999999999999</v>
@@ -701,34 +720,36 @@
         <v>0.47449999999999998</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5">
         <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="2">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5">
         <v>0.61370839420000001</v>
       </c>
-      <c r="K5" s="2">
+      <c r="M5">
         <v>0.87077697679999999</v>
       </c>
-      <c r="L5" s="3">
+      <c r="N5">
         <v>0.35663981150000001</v>
       </c>
-      <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0.68799999999999994</v>
@@ -740,27 +761,70 @@
         <v>0.47360000000000002</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G6">
         <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="2">
+        <v>34</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6">
         <v>0.61517095129999999</v>
       </c>
-      <c r="K6" s="3">
+      <c r="M6">
         <v>0.8708219358</v>
       </c>
-      <c r="L6" s="3">
+      <c r="N6">
         <v>0.35951996679999998</v>
       </c>
-      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7">
+        <v>0.60870000000000002</v>
+      </c>
+      <c r="D7">
+        <v>0.85680000000000001</v>
+      </c>
+      <c r="E7">
+        <v>0.36059999999999998</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>23.98</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.62893021429999996</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.86392371040000004</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.39393671810000003</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/752fb57b23291faf/문서/contest/wind_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_2B59D2BFD370D55035E0D9F0509718755DD5E2DC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894A9AE0-A1FE-464B-BC9E-263056E358BA}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_46C971B4D390DC0EED82C9F0505ED87656CDB6AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE34CC7E-DDC7-447E-9A69-9C0BFD1A03EE}"/>
   <bookViews>
-    <workbookView xWindow="6910" yWindow="5050" windowWidth="36270" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6840" yWindow="4440" windowWidth="36270" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="79">
   <si>
     <t>Timestamp</t>
   </si>
@@ -28,6 +28,21 @@
     <t>Version</t>
   </si>
   <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>ES Mode</t>
+  </si>
+  <si>
+    <t>Post Mode</t>
+  </si>
+  <si>
+    <t>Raw OOF</t>
+  </si>
+  <si>
     <t>Val_Total Score</t>
   </si>
   <si>
@@ -37,15 +52,36 @@
     <t>Val_FICR</t>
   </si>
   <si>
+    <t>Year Spread</t>
+  </si>
+  <si>
+    <t>Public LB</t>
+  </si>
+  <si>
+    <t>Private LB</t>
+  </si>
+  <si>
+    <t>Execution Time (sec)</t>
+  </si>
+  <si>
     <t>Model</t>
   </si>
   <si>
+    <t>Device</t>
+  </si>
+  <si>
     <t>Seed</t>
   </si>
   <si>
+    <t>N Features</t>
+  </si>
+  <si>
     <t>Features</t>
   </si>
   <si>
+    <t>Environment Spec</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -58,21 +94,27 @@
     <t>Leaderboard_FiCR</t>
   </si>
   <si>
-    <t>Execution Time (sec)</t>
-  </si>
-  <si>
     <t>2026-07-22 22:06:44</t>
   </si>
   <si>
     <t>v1</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>RandomForest</t>
   </si>
   <si>
+    <t>CPU</t>
+  </si>
+  <si>
     <t>기본 달력 피처 + GFS 80m 합성 풍속</t>
   </si>
   <si>
+    <t>CPU: AMD Ryzen 9 7950X | GPU: RTX 4080 SUPER | RAM: DDR5 64GB</t>
+  </si>
+  <si>
     <t>베이스라인 모듈화 및 로거 연동 테스트</t>
   </si>
   <si>
@@ -136,22 +178,85 @@
     <t>XGBoost</t>
   </si>
   <si>
+    <t>GPU</t>
+  </si>
+  <si>
     <t>v5 피처 + WPD/850hPa/De-rating/푄현상 등 6대 도메인 피처 + 35개 Pruning + Nelder-Mead 후처리</t>
   </si>
   <si>
     <t>5-Fold GroupKFold(월별) / Nelder-Mead 후처리 적용 (+0.0542)</t>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Environment Spec</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU: AMD Ryzen 9 7950X | GPU: RTX 4080 SUPER | RAM: DDR5 64GB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>2026-07-25 22:20:39</t>
+  </si>
+  <si>
+    <t>v7</t>
+  </si>
+  <si>
+    <t>v6 동일 피처 (6대 도메인 피처 + 35개 Pruning)</t>
+  </si>
+  <si>
+    <t>v7: v6 피처 파이프라인 기반 LightGBM 모델 교체 및 OOF 평가 (CPU 32쓰레드 병렬)</t>
+  </si>
+  <si>
+    <t>2026-07-25 22:35:47</t>
+  </si>
+  <si>
+    <t>v8</t>
+  </si>
+  <si>
+    <t>CatBoost</t>
+  </si>
+  <si>
+    <t>v8: v6 피처 파이프라인 기반 CatBoost (CPU 32스레드 가속) 모델 교체 및 OOF 평가</t>
+  </si>
+  <si>
+    <t>2026-07-25 23:10:28</t>
+  </si>
+  <si>
+    <t>v9</t>
+  </si>
+  <si>
+    <t>Ensemble(XGB+LGBM+CAT)</t>
+  </si>
+  <si>
+    <t>v6/v7/v8 앙상블 (가중치: 0.13/0.02/0.85)</t>
+  </si>
+  <si>
+    <t>v9: XGBoost+LightGBM+CatBoost OOF 최적 가중 앙상블 + Nelder-Mead 재최적화 (+0.0386)</t>
+  </si>
+  <si>
+    <t>2026-07-25 23:21:00</t>
+  </si>
+  <si>
+    <t>v10</t>
+  </si>
+  <si>
+    <t>v10: 원본 예측치 가중 결합 후 Nelder-Mead 단일 후처리 적용 (기존 이중 후처리 오류 수정 +0.0386)</t>
+  </si>
+  <si>
+    <t>2026-07-26 02:44:56</t>
+  </si>
+  <si>
+    <t>v11</t>
+  </si>
+  <si>
+    <t>loyo</t>
+  </si>
+  <si>
+    <t>clean_cf</t>
+  </si>
+  <si>
+    <t>refit</t>
+  </si>
+  <si>
+    <t>piecewise</t>
+  </si>
+  <si>
+    <t>v6 6대 물리/도메인 피처(WPD·850hPa 유입·De-rating·푄현상) + 35개 Pruning + SCADA 가동률 보정 정제 타깃(cf) + piecewise 단조 후처리</t>
+  </si>
+  <si>
+    <t>v11: SCADA(157,819+105,264행) 시각정렬 확정(vestas +50분 / unison +60분, R²=0.9993/0.9985) 후 가동률 마스크 산출 → 정비정지 4.2%/3.8%, 출력제한 1.7%/2.6% 를 학습 타깃에서 정규화. 타깃을 cf = label/(k×가용용량) 으로 교체(k: G1 0.9857 / G2 0.9893 / G3 1.0009). 검증을 월 GroupKFold → LOYO 로 교체하고 early stopping 누설 차단(내부 블록 ES + refit). 후처리는 Nelder-Mead 초기 simplex 스케일 버그 수정 + 구간별 단조 보정으로 교체. A/B 통제실험 결과 정제 타깃이 raw +0.0126 (3개 연도 전부 동일 부호, 표준편차 0.0043) 우세.  ⟨검증: LOYO(연 단위) — 테스트(2025 통째)와 동일 구조. month_group 과 절대값 비교 불가⟩</t>
   </si>
 </sst>
 </file>
@@ -208,12 +313,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -229,10 +333,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,20 +620,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="7.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="80.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="63.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.58203125" customWidth="1"/>
-    <col min="14" max="14" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="255.58203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.4140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.58203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,268 +658,587 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>0.7137</v>
+      </c>
+      <c r="I2">
+        <v>0.91490000000000005</v>
+      </c>
+      <c r="J2">
+        <v>0.51259999999999994</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2">
+        <v>0.5932059435</v>
+      </c>
+      <c r="W2">
+        <v>0.86146538110000004</v>
+      </c>
+      <c r="X2">
+        <v>0.32494650590000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3">
+        <v>0.79930000000000001</v>
+      </c>
+      <c r="I3">
+        <v>0.9355</v>
+      </c>
+      <c r="J3">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3">
+        <v>42</v>
+      </c>
+      <c r="S3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3">
+        <v>0.60208994459999998</v>
+      </c>
+      <c r="W3">
+        <v>0.86394474160000001</v>
+      </c>
+      <c r="X3">
+        <v>0.3402351475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4">
+        <v>0.68640000000000001</v>
+      </c>
+      <c r="I4">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="J4">
+        <v>0.4708</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4">
+        <v>42</v>
+      </c>
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" t="s">
+        <v>30</v>
+      </c>
+      <c r="U4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4">
+        <v>0.60569102330000002</v>
+      </c>
+      <c r="W4">
+        <v>0.86602318869999995</v>
+      </c>
+      <c r="X4">
+        <v>0.34535885789999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>41</v>
       </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5">
+        <v>0.68859999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0.90259999999999996</v>
+      </c>
+      <c r="J5">
+        <v>0.47449999999999998</v>
+      </c>
+      <c r="N5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5">
+        <v>42</v>
+      </c>
+      <c r="S5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V5">
+        <v>0.61370839420000001</v>
+      </c>
+      <c r="W5">
+        <v>0.87077697679999999</v>
+      </c>
+      <c r="X5">
+        <v>0.35663981150000001</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>0.7137</v>
-      </c>
-      <c r="D2">
-        <v>0.91490000000000005</v>
-      </c>
-      <c r="E2">
-        <v>0.51259999999999994</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="I6">
+        <v>0.90249999999999997</v>
+      </c>
+      <c r="J6">
+        <v>0.47360000000000002</v>
+      </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6">
         <v>42</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="S6" t="s">
+        <v>47</v>
+      </c>
+      <c r="T6" t="s">
+        <v>30</v>
+      </c>
+      <c r="U6" t="s">
+        <v>48</v>
+      </c>
+      <c r="V6">
+        <v>0.61517095129999999</v>
+      </c>
+      <c r="W6">
+        <v>0.8708219358</v>
+      </c>
+      <c r="X6">
+        <v>0.35951996679999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>0.60870000000000002</v>
+      </c>
+      <c r="I7">
+        <v>0.85680000000000001</v>
+      </c>
+      <c r="J7">
+        <v>0.36059999999999998</v>
+      </c>
+      <c r="N7">
+        <v>23.98</v>
+      </c>
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7">
         <v>42</v>
       </c>
-      <c r="L2">
-        <v>0.5932059435</v>
-      </c>
-      <c r="M2">
-        <v>0.86146538110000004</v>
-      </c>
-      <c r="N2">
-        <v>0.32494650590000002</v>
+      <c r="S7" t="s">
+        <v>53</v>
+      </c>
+      <c r="T7" t="s">
+        <v>30</v>
+      </c>
+      <c r="U7" t="s">
+        <v>54</v>
+      </c>
+      <c r="V7">
+        <v>0.62893021429999996</v>
+      </c>
+      <c r="W7">
+        <v>0.86392371040000004</v>
+      </c>
+      <c r="X7">
+        <v>0.39393671810000003</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>0.79930000000000001</v>
-      </c>
-      <c r="D3">
-        <v>0.9355</v>
-      </c>
-      <c r="E3">
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8">
+        <v>0.59250000000000003</v>
+      </c>
+      <c r="I8">
+        <v>0.85070000000000001</v>
+      </c>
+      <c r="J8">
+        <v>0.33429999999999999</v>
+      </c>
+      <c r="N8">
+        <v>126.81</v>
+      </c>
+      <c r="O8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8">
         <v>42</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3">
-        <v>0.60208994459999998</v>
-      </c>
-      <c r="M3">
-        <v>0.86394474160000001</v>
-      </c>
-      <c r="N3">
-        <v>0.3402351475</v>
+      <c r="S8" t="s">
+        <v>57</v>
+      </c>
+      <c r="T8" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" t="s">
+        <v>58</v>
+      </c>
+      <c r="V8">
+        <v>0.61402080410000004</v>
+      </c>
+      <c r="W8">
+        <v>0.86127274200000004</v>
+      </c>
+      <c r="X8">
+        <v>0.36676886619999999</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4">
-        <v>0.68640000000000001</v>
-      </c>
-      <c r="D4">
-        <v>0.90200000000000002</v>
-      </c>
-      <c r="E4">
-        <v>0.4708</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9">
+        <v>0.61029999999999995</v>
+      </c>
+      <c r="I9">
+        <v>0.85550000000000004</v>
+      </c>
+      <c r="J9">
+        <v>0.36509999999999998</v>
+      </c>
+      <c r="N9">
+        <v>63.02</v>
+      </c>
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+      <c r="P9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9">
         <v>42</v>
       </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4">
-        <v>0.60569102330000002</v>
-      </c>
-      <c r="M4">
-        <v>0.86602318869999995</v>
-      </c>
-      <c r="N4">
-        <v>0.34535885789999998</v>
+      <c r="S9" t="s">
+        <v>57</v>
+      </c>
+      <c r="T9" t="s">
+        <v>30</v>
+      </c>
+      <c r="U9" t="s">
+        <v>62</v>
+      </c>
+      <c r="V9">
+        <v>0.61887448730000005</v>
+      </c>
+      <c r="W9">
+        <v>0.85930257330000004</v>
+      </c>
+      <c r="X9">
+        <v>0.37844640130000001</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>0.68859999999999999</v>
-      </c>
-      <c r="D5">
-        <v>0.90259999999999996</v>
-      </c>
-      <c r="E5">
-        <v>0.47449999999999998</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10">
+        <v>0.61180000000000001</v>
+      </c>
+      <c r="I10">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="J10">
+        <v>0.36830000000000002</v>
+      </c>
+      <c r="N10">
+        <v>5.13</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10">
         <v>42</v>
       </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="S10" t="s">
+        <v>66</v>
+      </c>
+      <c r="T10" t="s">
         <v>30</v>
       </c>
-      <c r="J5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5">
-        <v>0.61370839420000001</v>
-      </c>
-      <c r="M5">
-        <v>0.87077697679999999</v>
-      </c>
-      <c r="N5">
-        <v>0.35663981150000001</v>
+      <c r="U10" t="s">
+        <v>67</v>
+      </c>
+      <c r="V10">
+        <v>0.54985750450000004</v>
+      </c>
+      <c r="W10">
+        <v>0.8133095078</v>
+      </c>
+      <c r="X10">
+        <v>0.28640550110000002</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6">
-        <v>0.68799999999999994</v>
-      </c>
-      <c r="D6">
-        <v>0.90249999999999997</v>
-      </c>
-      <c r="E6">
-        <v>0.47360000000000002</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11">
+        <v>0.61180000000000001</v>
+      </c>
+      <c r="I11">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="J11">
+        <v>0.36830000000000002</v>
+      </c>
+      <c r="N11">
+        <v>0.24</v>
+      </c>
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11">
         <v>42</v>
       </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6">
-        <v>0.61517095129999999</v>
-      </c>
-      <c r="M6">
-        <v>0.8708219358</v>
-      </c>
-      <c r="N6">
-        <v>0.35951996679999998</v>
+      <c r="S11" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" t="s">
+        <v>30</v>
+      </c>
+      <c r="U11" t="s">
+        <v>70</v>
+      </c>
+      <c r="V11">
+        <v>0.61847564030000002</v>
+      </c>
+      <c r="W11">
+        <v>0.85872639350000002</v>
+      </c>
+      <c r="X11">
+        <v>0.37822488700000001</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <v>0.60870000000000002</v>
-      </c>
-      <c r="D7">
-        <v>0.85680000000000001</v>
-      </c>
-      <c r="E7">
-        <v>0.36059999999999998</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="H12">
+        <v>0.61560000000000004</v>
+      </c>
+      <c r="I12">
+        <v>0.86029999999999995</v>
+      </c>
+      <c r="J12">
+        <v>0.37080000000000002</v>
+      </c>
+      <c r="K12">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="N12">
+        <v>80.66</v>
+      </c>
+      <c r="O12" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12">
         <v>42</v>
       </c>
-      <c r="H7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>23.98</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0.62893021429999996</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.86392371040000004</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0.39393671810000003</v>
+      <c r="R12">
+        <v>812</v>
+      </c>
+      <c r="S12" t="s">
+        <v>77</v>
+      </c>
+      <c r="T12" t="s">
+        <v>30</v>
+      </c>
+      <c r="U12" t="s">
+        <v>78</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.63631627589999995</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.86488952509999995</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0.40774302670000001</v>
       </c>
     </row>
   </sheetData>
